--- a/Measurements/3222610 WHL, RAD FIN 6.5x2x2.625/3222610_v2.xlsx
+++ b/Measurements/3222610 WHL, RAD FIN 6.5x2x2.625/3222610_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoe\Meng\solidworks\Measurements\3222610 WHL, RAD FIN 6.5x2x2.625\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCA8A95-AB53-4FA5-91BF-DF03D53B70D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390DE313-850D-49E2-AA97-4C390B4CB243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
   </bookViews>
   <sheets>
     <sheet name="FAI" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Customer</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>Caliper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -555,17 +558,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1718,7 +1711,7 @@
     <mergeCell ref="G1:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="I5:I8">
-    <cfRule type="cellIs" dxfId="1" priority="22" operator="notBetween">
+    <cfRule type="cellIs" dxfId="0" priority="22" operator="notBetween">
       <formula>$G5</formula>
       <formula>$F5</formula>
     </cfRule>
@@ -1731,9 +1724,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9490EC76-6455-44B4-AA60-563ACC8D591D}">
-  <dimension ref="A1"/>
+  <dimension ref="Q23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="23" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
